--- a/02_加值成品/九上/九上4-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上4-3_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上4-3 電壓、電阻與歐姆定律　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三上學期 九上4-3 電壓、電阻與歐姆定律　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>驅動電流的電位差是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>加倍</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>歐姆(Ω)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>電流電壓電阻</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>電壓</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>推力</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>電壓的單位是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>伏特(V)</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>加倍</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>增大</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
           <t>電壓</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="34" customHeight="1">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>電壓</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>阻礙電流的程度是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>伏特(V)</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>越粗電阻越小</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>V=IR</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>電阻</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>阻力</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>電阻的單位是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>過原點直線</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>電壓</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>歐姆(Ω)</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>V=IR</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>電阻</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>歐姆定律公式是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>V=IR</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>電阻</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>電壓</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>伏特(V)</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>電壓電流電阻</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>測電壓的儀器是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>伏特計</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>越粗電阻越小</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>電阻</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>電壓</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>三用電表</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>伏特計要怎麼接？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>伏特計</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>電阻</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>歐姆(Ω)</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>並聯</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>並接</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>電阻越大電流？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>伏特計</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>伏特(V)</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>減半</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>越小</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>阻礙</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>電流受到的阻礙程度稱？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>伏特(V)</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>並聯</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>越長電阻越大</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>電阻</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>阻礙</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>歐姆定律電壓等於電流乘？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>電阻</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>電壓</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>V=IR</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>伏特計</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>V=IR</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上4-3 電壓、電阻與歐姆定律　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三上學期 九上4-3 電壓、電阻與歐姆定律　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>電壓6V電阻2Ω,電流？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>3 A</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>2 A</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>10 V</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>30 Ω</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>V/R</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>電流2A電阻5Ω,電壓？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>30 Ω</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>2 A</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>10 V</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>3 A</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>IR</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>電壓12V電流3A,電阻？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>2 A</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>24 Ω</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>10 V</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>4 Ω</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>V/I</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>定電阻下電壓加倍電流？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>加倍</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>電壓</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>並聯</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>電阻</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>正比</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>伏特計串聯還並聯？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>並聯</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>越長電阻越大</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>越粗電阻越小</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>電阻</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>接法</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>導體電阻與長度關係？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>伏特(V)</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>電流電壓電阻</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>並聯</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>越長電阻越大</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>正比</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>導體電阻與粗細關係？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>電阻</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>並聯</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>越粗電阻越小</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>V=IR</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>反比</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>三用電表可測哪些量？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>越粗電阻越小</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>電壓</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>電流電壓電阻</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>增大</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>多功能</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>電壓10V電阻5Ω電流？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>2 A</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>30 Ω</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>10 V</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>3 A</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>V/R</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>電流3A電阻4Ω電壓？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>12 V</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>10 V</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>3 A</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>4 Ω</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>IR</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上4-3 電壓、電阻與歐姆定律　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三上學期 九上4-3 電壓、電阻與歐姆定律　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>電壓9V使電流0.3A流過燈泡,電阻多少？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>10 V</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>3 A</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>30 Ω</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>4 Ω</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>V/I</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何伏特計並聯而安培計串聯？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>量電位差需並接兩端;量電流需串接</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>電流通過電阻發熱</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>移高中,國中重基本概念</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>測不同電壓下電流看V與I成正比</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>接法</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>定電阻導體V-I圖形是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>越小</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>過原點直線</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>V=IR</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>增大</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>線性</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>同材質導線變長變細電阻如何？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>增大</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>減半</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>電阻</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>電壓</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>長增粗減</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>電壓不變電阻加倍電流如何？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>減半</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>電壓</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>V=IR</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>過原點直線</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>反比</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>用三用電表如何驗證歐姆定律？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>移高中,國中重基本概念</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>電流通過電阻發熱</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>測不同電壓下電流看V與I成正比</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>量電位差需並接兩端;量電流需串接</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>實驗</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>電熱器利用電阻的什麼效應？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>電流通過電阻發熱</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>量電位差需並接兩端;量電流需串接</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>測不同電壓下電流看V與I成正比</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>移高中,國中重基本概念</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>熱效應</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>為何課綱刪串並聯公式計算？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>移高中,國中重基本概念</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>電流通過電阻發熱</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>量電位差需並接兩端;量電流需串接</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>越長越大、越粗越小</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>課綱</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>電壓12V電流0.5A電阻多少？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>10 V</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>2 A</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>24 Ω</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>3 A</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>V/I</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>導線越長電阻越?越粗電阻越?</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>測不同電壓下電流看V與I成正比</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>移高中,國中重基本概念</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>量電位差需並接兩端;量電流需串接</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>越長越大、越粗越小</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>長粗</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九上/九上4-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上4-3_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>推力</t>
+          <t>推力：電壓就像水位落差,是推動電荷流動形成電流的原因</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>電壓</t>
+          <t>電壓：科學上用伏特這個單位來表示電壓的大小</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>阻力</t>
+          <t>阻力：電阻是導線或元件阻礙電流通過的程度大小</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>電阻</t>
+          <t>電阻：科學上用歐姆這個單位來表示電阻的大小</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>電壓電流電阻</t>
+          <t>電壓電流電阻：電壓等於電流乘以電阻,這就是歐姆定律的公式</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>三用電表</t>
+          <t>三用電表：伏特計是專門用來測量電路中電壓大小的儀器</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>並接</t>
+          <t>並接：伏特計要接在待測元件的兩端,和元件並排連接才能量出電壓</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>阻礙</t>
+          <t>阻礙：電阻越大代表對電流的阻礙越強,通過的電流就會變小</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>阻礙</t>
+          <t>阻礙：導線或元件對電流通過造成的阻礙程度稱為電阻,電阻越大電流越不容易通過</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>V=IR</t>
+          <t>V=IR：歐姆定律的公式是電壓=電流×電阻,寫成V=IR</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>V/R</t>
+          <t>V/R：歐姆定律I=V/R,把電壓6V除以電阻2Ω等於3安培</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>IR</t>
+          <t>IR：把電流2安培乘以電阻5歐姆,等於電壓10伏特</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>V/I</t>
+          <t>V/I：把電壓12伏特除以電流3安培,等於電阻4歐姆</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>正比</t>
+          <t>正比：電阻固定不變時,電壓變成兩倍,電流也會跟著變成兩倍</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>接法</t>
+          <t>接法：伏特計要並聯接在元件兩端,才能正確量出兩端的電壓差</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>正比</t>
+          <t>正比：導線越長,電子要通過的距離越遠,受到的阻礙也越大</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>反比</t>
+          <t>反比：導線越粗,可通過的空間越大,電子越容易通過,電阻就越小</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>多功能</t>
+          <t>多功能：一台三用電表切換檔位後,可以分別測量電流、電壓和電阻</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>V/R</t>
+          <t>V/R：由歐姆定律I=V/R,10伏特除以5歐姆等於2安培</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>IR</t>
+          <t>IR：由歐姆定律V=IR,3安培乘以4歐姆等於12伏特</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>V/I</t>
+          <t>V/I：把電壓9伏特除以電流0.3安培,算出這個燈泡的電阻是30歐姆</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>接法</t>
+          <t>接法：伏特計要量兩點間的電位差所以並接在兩端,安培計要量通過的電流所以要串在電路裡讓電流流經它</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>線性</t>
+          <t>線性：電阻固定時電壓和電流成正比,畫出來會是一條經過原點的直線</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>長增粗減</t>
+          <t>長增粗減：導線變長會讓電阻變大,同時變細也會讓電阻變大,兩個效果加在一起電阻明顯增大</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>反比</t>
+          <t>反比：電壓固定不變的情況下,把電阻變成兩倍,電流就會變成原來的一半</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>實驗</t>
+          <t>實驗：改變電壓的大小,分別測量對應的電流值,再看看兩者的比值是否維持固定</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>熱效應</t>
+          <t>熱效應：電流流過電阻大的發熱線圈時會產生大量熱能,這就是電熱器發熱的原理</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>課綱</t>
+          <t>課綱：串並聯電路的詳細計算比較複雜,課程安排把它移到高中,國中先建立基本概念就好</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>V/I</t>
+          <t>V/I：由歐姆定律R=V/I,12伏特除以0.5安培等於24歐姆</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>長粗</t>
+          <t>長粗：導線越長,電子要通過的路徑越長,電阻越大;導線越粗,可通過的截面積越大,電阻越小</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九上/九上4-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上4-3_三種難度測驗卷.xlsx
@@ -563,17 +563,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>加倍</t>
+          <t>減半</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>越長電阻越大</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
           <t>歐姆(Ω)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>電流電壓電阻</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -643,17 +643,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>伏特(V)</t>
+          <t>電壓</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>越粗電阻越小</t>
+          <t>減半</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>V=IR</t>
+          <t>過原點直線</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -843,17 +843,17 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
+          <t>電壓</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>電阻</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
           <t>伏特計</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>伏特(V)</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>減半</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -883,17 +883,17 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>伏特(V)</t>
+          <t>伏特計</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>並聯</t>
+          <t>歐姆(Ω)</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>越長電阻越大</t>
+          <t>增大</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
+          <t>V=IR</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
           <t>電壓</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>V=IR</t>
-        </is>
-      </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>伏特計</t>
+          <t>伏特(V)</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1119,17 +1119,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
+          <t>10 V</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
           <t>2 A</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>24 Ω</t>
-        </is>
-      </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>10 V</t>
+          <t>3 A</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>伏特(V)</t>
+          <t>歐姆(Ω)</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>電流電壓電阻</t>
+          <t>越粗電阻越小</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>並聯</t>
+          <t>伏特計</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -1279,12 +1279,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>電阻</t>
+          <t>V=IR</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>並聯</t>
+          <t>電壓</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>V=IR</t>
+          <t>加倍</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>電壓</t>
+          <t>越小</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>增大</t>
+          <t>伏特(V)</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>10 V</t>
+          <t>2 A</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>2 A</t>
+          <t>30 Ω</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>3 A</t>
+          <t>12 V</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
